--- a/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </sheets>
 </workbook>
 </file>
@@ -38,9 +38,9 @@
     </border>
   </borders>
   <cellXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>

--- a/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
@@ -92,5 +92,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:B3"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B3">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
--- a/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
@@ -93,7 +93,7 @@
   </sheetData>
   <autoFilter ref="A1:B3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="B2:B3">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
@@ -1,14 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\Excelsior\src\StaticSettingsTests\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E8A6FF603911C934C06F23E596C72BFEC18C6A5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="5016" yWindow="3324" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Is Active</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -37,65 +72,384 @@
       <diagonal/>
     </border>
   </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
   <cellXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Is Active</t>
-        </is>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Alice</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bob</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="B2:B3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="B2:B3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/VerifyTests/Verify.OpenXml/v1/columnMetadata">
+  <sheet name="Sheet1">
+    <column index="1" property="Name"/>
+    <column index="2" property="IsActive"/>
+  </sheet>
+</columnMetadata>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDA9357-735B-48B7-921D-4D2369C95322}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://github.com/VerifyTests/Verify.OpenXml/v1/columnMetadata"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
@@ -9,6 +9,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[=1]&quot;Yes&quot;;[=0]&quot;No&quot;"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -37,10 +40,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -78,15 +84,11 @@
           <t xml:space="preserve">Alice</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
+      <c r="B2" s="3" t="b">
+        <v>1</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
+      <c r="C2" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -95,15 +97,11 @@
           <t xml:space="preserve">Bob</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
+      <c r="B3" s="3" t="b">
+        <v>0</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No</t>
-        </is>
+      <c r="C3" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -112,12 +110,14 @@
           <t xml:space="preserve">Carol</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C4"/>

--- a/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
@@ -2,13 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[=1]&quot;Yes&quot;;[=0]&quot;No&quot;"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -37,10 +40,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -52,6 +58,7 @@
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -65,6 +72,11 @@
           <t xml:space="preserve">Is Active</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Is Admin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -72,10 +84,11 @@
           <t xml:space="preserve">Alice</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
+      <c r="B2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -84,13 +97,47 @@
           <t xml:space="preserve">Bob</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Carol</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:C4"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Yes, No." sqref="B2:B4">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Yes, No." sqref="C2:C4">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Name"/>
+    <column index="2" property="IsActive"/>
+    <column index="3" property="IsAdmin"/>
+  </sheet>
+</columnMetadata>
 </file>